--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-traitements.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-traitements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-traitements.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-traitements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-traitements.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-traitements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-traitements.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-traitements.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$86</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2374" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2725" uniqueCount="296">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -532,10 +532,13 @@
     <t>Section.id</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Identifiant de la section</t>
+  </si>
+  <si>
     <t>Section.code</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CE
@@ -543,6 +546,148 @@
   </si>
   <si>
     <t>Code de la section</t>
+  </si>
+  <si>
+    <t>Section.code.nullFlavor</t>
+  </si>
+  <si>
+    <t>Section.code.code</t>
+  </si>
+  <si>
+    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
+  </si>
+  <si>
+    <t>10160-0</t>
+  </si>
+  <si>
+    <t>CD.code</t>
+  </si>
+  <si>
+    <t>Section.code.codeSystem</t>
+  </si>
+  <si>
+    <t>Code System</t>
+  </si>
+  <si>
+    <t>Specifies the code system that defines the code.</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.6.1</t>
+  </si>
+  <si>
+    <t>CD.codeSystem</t>
+  </si>
+  <si>
+    <t>Section.code.codeSystemName</t>
+  </si>
+  <si>
+    <t>Code System Name</t>
+  </si>
+  <si>
+    <t>The common name of the coding system.</t>
+  </si>
+  <si>
+    <t>LOINC</t>
+  </si>
+  <si>
+    <t>CD.codeSystemName</t>
+  </si>
+  <si>
+    <t>Section.code.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Code System Version</t>
+  </si>
+  <si>
+    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Section.code.displayName</t>
+  </si>
+  <si>
+    <t>Display Name</t>
+  </si>
+  <si>
+    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
+  </si>
+  <si>
+    <t>Traitements</t>
+  </si>
+  <si>
+    <t>CD.displayName</t>
+  </si>
+  <si>
+    <t>Section.code.sdtcValueSet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
+</t>
+  </si>
+  <si>
+    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.valueSet</t>
+  </si>
+  <si>
+    <t>Section.code.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>Section.code.originalText</t>
+  </si>
+  <si>
+    <t>Original Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
+</t>
+  </si>
+  <si>
+    <t>The text or phrase used as the basis for the coding.</t>
+  </si>
+  <si>
+    <t>CD.originalText</t>
+  </si>
+  <si>
+    <t>Section.code.qualifier</t>
+  </si>
+  <si>
+    <t>Qualifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
+</t>
+  </si>
+  <si>
+    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
+  </si>
+  <si>
+    <t>CD.qualifier</t>
+  </si>
+  <si>
+    <t>Section.code.translation</t>
+  </si>
+  <si>
+    <t>Translation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CD
+</t>
+  </si>
+  <si>
+    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
+  </si>
+  <si>
+    <t>CD.translation</t>
   </si>
   <si>
     <t>Section.title</t>
@@ -1107,7 +1252,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK75"/>
+  <dimension ref="A1:AK86"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="54.17578125" customWidth="true" bestFit="true"/>
@@ -4426,7 +4571,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>167</v>
       </c>
@@ -4445,7 +4590,7 @@
         <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>74</v>
@@ -4456,8 +4601,12 @@
       <c r="K33" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
+      <c r="L33" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>169</v>
+      </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4527,10 +4676,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4544,7 +4693,7 @@
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
@@ -4553,13 +4702,13 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4610,7 +4759,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4628,26 +4777,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E35" s="2"/>
+      <c r="E35" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F35" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>169</v>
+        <v>74</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>74</v>
@@ -4656,13 +4807,11 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>174</v>
+        <v>86</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4689,13 +4838,11 @@
         <v>74</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>74</v>
@@ -4713,7 +4860,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>172</v>
+        <v>89</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4733,16 +4880,18 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E36" s="2"/>
+      <c r="E36" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F36" t="s" s="2">
         <v>75</v>
       </c>
@@ -4750,7 +4899,7 @@
         <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>74</v>
@@ -4759,13 +4908,11 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4777,7 +4924,7 @@
         <v>74</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>74</v>
+        <v>176</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>74</v>
@@ -4816,7 +4963,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4834,7 +4981,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>178</v>
       </c>
@@ -4845,15 +4992,17 @@
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E37" s="2"/>
+      <c r="E37" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>74</v>
@@ -4862,10 +5011,12 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>170</v>
+        <v>112</v>
       </c>
       <c r="L37" s="2"/>
-      <c r="M37" s="2"/>
+      <c r="M37" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -4876,7 +5027,7 @@
         <v>74</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>74</v>
+        <v>181</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>74</v>
@@ -4915,7 +5066,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -4935,16 +5086,18 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E38" s="2"/>
+      <c r="E38" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
@@ -4961,10 +5114,12 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
+      <c r="M38" t="s" s="2">
+        <v>185</v>
+      </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -4975,7 +5130,7 @@
         <v>74</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>74</v>
+        <v>186</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>74</v>
@@ -4990,11 +5145,13 @@
         <v>74</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y38" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z38" t="s" s="2">
-        <v>180</v>
+        <v>74</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>74</v>
@@ -5012,7 +5169,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5032,16 +5189,18 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E39" s="2"/>
+      <c r="E39" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
@@ -5058,10 +5217,12 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>182</v>
+        <v>102</v>
       </c>
       <c r="L39" s="2"/>
-      <c r="M39" s="2"/>
+      <c r="M39" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5111,7 +5272,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5129,26 +5290,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E40" s="2"/>
+      <c r="E40" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -5157,10 +5320,12 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>184</v>
+        <v>102</v>
       </c>
       <c r="L40" s="2"/>
-      <c r="M40" s="2"/>
+      <c r="M40" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5171,7 +5336,7 @@
         <v>74</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>74</v>
+        <v>195</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>74</v>
@@ -5210,13 +5375,13 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>74</v>
@@ -5230,10 +5395,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5244,7 +5409,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>74</v>
@@ -5256,10 +5421,12 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="L41" s="2"/>
-      <c r="M41" s="2"/>
+      <c r="M41" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -5309,13 +5476,13 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>74</v>
@@ -5327,12 +5494,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5340,13 +5507,13 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>169</v>
+        <v>74</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>74</v>
@@ -5355,12 +5522,12 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="M42" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="L42" s="2"/>
+      <c r="M42" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -5410,13 +5577,13 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>74</v>
@@ -5430,17 +5597,17 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>84</v>
+        <v>205</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
@@ -5458,11 +5625,11 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>85</v>
+        <v>206</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>86</v>
+        <v>207</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5489,11 +5656,13 @@
         <v>74</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y43" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z43" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>74</v>
@@ -5511,7 +5680,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>89</v>
+        <v>208</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5531,21 +5700,23 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E44" s="2"/>
+      <c r="E44" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>74</v>
@@ -5557,11 +5728,11 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>91</v>
+        <v>211</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>92</v>
+        <v>212</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5612,7 +5783,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>93</v>
+        <v>213</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5632,21 +5803,23 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E45" s="2"/>
+      <c r="E45" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>74</v>
@@ -5658,11 +5831,11 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>95</v>
+        <v>216</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>96</v>
+        <v>217</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5713,46 +5886,44 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>97</v>
+        <v>218</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>193</v>
+        <v>219</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>193</v>
+        <v>219</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E46" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>74</v>
@@ -5761,11 +5932,13 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L46" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="M46" t="s" s="2">
-        <v>86</v>
+        <v>221</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5792,11 +5965,13 @@
         <v>74</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y46" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z46" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>74</v>
@@ -5814,7 +5989,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>89</v>
+        <v>219</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -5832,28 +6007,26 @@
         <v>74</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E47" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>
@@ -5862,11 +6035,13 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L47" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="M47" t="s" s="2">
-        <v>103</v>
+        <v>224</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -5917,7 +6092,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>104</v>
+        <v>222</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -5937,18 +6112,16 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E48" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
@@ -5965,12 +6138,10 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>107</v>
+        <v>171</v>
       </c>
       <c r="L48" s="2"/>
-      <c r="M48" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M48" s="2"/>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6020,7 +6191,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>109</v>
+        <v>225</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6040,20 +6211,18 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E49" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>75</v>
@@ -6068,12 +6237,10 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="L49" s="2"/>
-      <c r="M49" t="s" s="2">
-        <v>113</v>
-      </c>
+      <c r="M49" s="2"/>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6081,7 +6248,7 @@
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>74</v>
@@ -6099,13 +6266,11 @@
         <v>74</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>74</v>
+        <v>227</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>74</v>
@@ -6123,7 +6288,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>115</v>
+        <v>226</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6143,20 +6308,18 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E50" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>75</v>
@@ -6171,12 +6334,10 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>102</v>
+        <v>229</v>
       </c>
       <c r="L50" s="2"/>
-      <c r="M50" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="M50" s="2"/>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -6226,7 +6387,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>119</v>
+        <v>228</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6246,10 +6407,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6272,12 +6433,10 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>95</v>
+        <v>231</v>
       </c>
       <c r="L51" s="2"/>
-      <c r="M51" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M51" s="2"/>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -6327,7 +6486,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>125</v>
+        <v>230</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6347,10 +6506,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>199</v>
+        <v>232</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>199</v>
+        <v>232</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6361,7 +6520,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>74</v>
@@ -6373,14 +6532,14 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>85</v>
+        <v>233</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
-        <v>200</v>
+        <v>74</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
@@ -6402,11 +6561,13 @@
         <v>74</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y52" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z52" t="s" s="2">
-        <v>201</v>
+        <v>74</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>74</v>
@@ -6424,13 +6585,13 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>202</v>
+        <v>232</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>74</v>
@@ -6442,12 +6603,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>203</v>
+        <v>234</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>203</v>
+        <v>234</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6455,13 +6616,13 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>74</v>
@@ -6470,9 +6631,11 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L53" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6481,7 +6644,7 @@
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
-        <v>204</v>
+        <v>74</v>
       </c>
       <c r="S53" t="s" s="2">
         <v>74</v>
@@ -6523,13 +6686,13 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>205</v>
+        <v>234</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>74</v>
@@ -6543,16 +6706,18 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>206</v>
+        <v>237</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>206</v>
+        <v>237</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E54" s="2"/>
+      <c r="E54" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
@@ -6569,10 +6734,12 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>207</v>
+        <v>85</v>
       </c>
       <c r="L54" s="2"/>
-      <c r="M54" s="2"/>
+      <c r="M54" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -6598,13 +6765,11 @@
         <v>74</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>74</v>
@@ -6622,7 +6787,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>208</v>
+        <v>89</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6642,10 +6807,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>209</v>
+        <v>238</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>209</v>
+        <v>238</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6656,7 +6821,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>74</v>
@@ -6668,10 +6833,12 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>210</v>
+        <v>91</v>
       </c>
       <c r="L55" s="2"/>
-      <c r="M55" s="2"/>
+      <c r="M55" t="s" s="2">
+        <v>92</v>
+      </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -6721,13 +6888,13 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>211</v>
+        <v>93</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>74</v>
@@ -6741,10 +6908,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>212</v>
+        <v>239</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>212</v>
+        <v>239</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6767,10 +6934,12 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>213</v>
+        <v>95</v>
       </c>
       <c r="L56" s="2"/>
-      <c r="M56" s="2"/>
+      <c r="M56" t="s" s="2">
+        <v>96</v>
+      </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -6820,7 +6989,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>214</v>
+        <v>97</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -6832,7 +7001,7 @@
         <v>74</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>74</v>
@@ -6840,16 +7009,18 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E57" s="2"/>
+      <c r="E57" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
@@ -6866,10 +7037,12 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>216</v>
+        <v>85</v>
       </c>
       <c r="L57" s="2"/>
-      <c r="M57" s="2"/>
+      <c r="M57" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -6895,13 +7068,11 @@
         <v>74</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>74</v>
@@ -6919,7 +7090,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>217</v>
+        <v>89</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -6939,16 +7110,18 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E58" s="2"/>
+      <c r="E58" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
@@ -6965,10 +7138,12 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>219</v>
+        <v>102</v>
       </c>
       <c r="L58" s="2"/>
-      <c r="M58" s="2"/>
+      <c r="M58" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7018,7 +7193,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>220</v>
+        <v>104</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7038,16 +7213,18 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E59" s="2"/>
+      <c r="E59" t="s" s="2">
+        <v>106</v>
+      </c>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
@@ -7064,10 +7241,12 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>222</v>
+        <v>107</v>
       </c>
       <c r="L59" s="2"/>
-      <c r="M59" s="2"/>
+      <c r="M59" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -7117,7 +7296,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>223</v>
+        <v>109</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7137,18 +7316,20 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E60" s="2"/>
+      <c r="E60" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="F60" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>75</v>
@@ -7163,10 +7344,12 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>225</v>
+        <v>112</v>
       </c>
       <c r="L60" s="2"/>
-      <c r="M60" s="2"/>
+      <c r="M60" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -7174,7 +7357,7 @@
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>74</v>
@@ -7216,7 +7399,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>226</v>
+        <v>115</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7236,18 +7419,20 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E61" s="2"/>
+      <c r="E61" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F61" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>75</v>
@@ -7262,10 +7447,12 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>228</v>
+        <v>102</v>
       </c>
       <c r="L61" s="2"/>
-      <c r="M61" s="2"/>
+      <c r="M61" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -7315,7 +7502,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>229</v>
+        <v>119</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7335,10 +7522,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7349,7 +7536,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>74</v>
@@ -7361,10 +7548,12 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>231</v>
+        <v>95</v>
       </c>
       <c r="L62" s="2"/>
-      <c r="M62" s="2"/>
+      <c r="M62" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -7414,13 +7603,13 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>232</v>
+        <v>125</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>74</v>
@@ -7434,10 +7623,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7448,7 +7637,7 @@
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>74</v>
@@ -7460,14 +7649,14 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>234</v>
+        <v>85</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" t="s" s="2">
@@ -7489,13 +7678,11 @@
         <v>74</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>74</v>
+        <v>248</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>74</v>
@@ -7513,13 +7700,13 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>74</v>
@@ -7533,18 +7720,16 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E64" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
@@ -7561,12 +7746,10 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="L64" s="2"/>
-      <c r="M64" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M64" s="2"/>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -7574,7 +7757,7 @@
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>74</v>
+        <v>251</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>74</v>
@@ -7592,11 +7775,13 @@
         <v>74</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y64" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z64" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>74</v>
@@ -7614,7 +7799,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>89</v>
+        <v>252</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -7634,10 +7819,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7648,7 +7833,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>74</v>
@@ -7660,12 +7845,10 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>91</v>
+        <v>254</v>
       </c>
       <c r="L65" s="2"/>
-      <c r="M65" t="s" s="2">
-        <v>92</v>
-      </c>
+      <c r="M65" s="2"/>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -7715,13 +7898,13 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>93</v>
+        <v>255</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>74</v>
@@ -7735,10 +7918,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -7761,12 +7944,10 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>95</v>
+        <v>257</v>
       </c>
       <c r="L66" s="2"/>
-      <c r="M66" t="s" s="2">
-        <v>96</v>
-      </c>
+      <c r="M66" s="2"/>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -7816,7 +7997,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>97</v>
+        <v>258</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -7828,7 +8009,7 @@
         <v>74</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>74</v>
@@ -7836,18 +8017,16 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E67" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>80</v>
       </c>
@@ -7864,12 +8043,10 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>85</v>
+        <v>260</v>
       </c>
       <c r="L67" s="2"/>
-      <c r="M67" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M67" s="2"/>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -7895,11 +8072,13 @@
         <v>74</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y67" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z67" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>74</v>
@@ -7917,7 +8096,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>89</v>
+        <v>261</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -7937,18 +8116,16 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E68" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
@@ -7965,12 +8142,10 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>102</v>
+        <v>263</v>
       </c>
       <c r="L68" s="2"/>
-      <c r="M68" t="s" s="2">
-        <v>103</v>
-      </c>
+      <c r="M68" s="2"/>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -8020,7 +8195,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>104</v>
+        <v>264</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8040,18 +8215,16 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E69" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
@@ -8068,12 +8241,10 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>107</v>
+        <v>266</v>
       </c>
       <c r="L69" s="2"/>
-      <c r="M69" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M69" s="2"/>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -8123,7 +8294,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>109</v>
+        <v>267</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8143,20 +8314,18 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>241</v>
+        <v>268</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>241</v>
+        <v>268</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E70" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>75</v>
@@ -8171,12 +8340,10 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>112</v>
+        <v>269</v>
       </c>
       <c r="L70" s="2"/>
-      <c r="M70" t="s" s="2">
-        <v>113</v>
-      </c>
+      <c r="M70" s="2"/>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -8184,7 +8351,7 @@
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>74</v>
@@ -8226,7 +8393,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>115</v>
+        <v>270</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8246,20 +8413,18 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E71" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>75</v>
@@ -8274,12 +8439,10 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>102</v>
+        <v>272</v>
       </c>
       <c r="L71" s="2"/>
-      <c r="M71" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="M71" s="2"/>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -8329,7 +8492,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>119</v>
+        <v>273</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8349,10 +8512,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>243</v>
+        <v>274</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>243</v>
+        <v>274</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8363,7 +8526,7 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>74</v>
@@ -8375,12 +8538,10 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>95</v>
+        <v>275</v>
       </c>
       <c r="L72" s="2"/>
-      <c r="M72" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M72" s="2"/>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -8430,13 +8591,13 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>125</v>
+        <v>276</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>74</v>
@@ -8450,10 +8611,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>244</v>
+        <v>277</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8476,12 +8637,10 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>85</v>
+        <v>278</v>
       </c>
       <c r="L73" s="2"/>
-      <c r="M73" t="s" s="2">
-        <v>245</v>
-      </c>
+      <c r="M73" s="2"/>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -8489,7 +8648,7 @@
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" t="s" s="2">
-        <v>200</v>
+        <v>74</v>
       </c>
       <c r="S73" t="s" s="2">
         <v>74</v>
@@ -8531,7 +8690,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>244</v>
+        <v>279</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8551,10 +8710,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>246</v>
+        <v>280</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>246</v>
+        <v>280</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8565,7 +8724,7 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>74</v>
@@ -8577,7 +8736,7 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>107</v>
+        <v>281</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -8588,7 +8747,7 @@
       </c>
       <c r="Q74" s="2"/>
       <c r="R74" t="s" s="2">
-        <v>204</v>
+        <v>74</v>
       </c>
       <c r="S74" t="s" s="2">
         <v>74</v>
@@ -8630,13 +8789,13 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>246</v>
+        <v>280</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>74</v>
@@ -8650,18 +8809,20 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>247</v>
+        <v>282</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>247</v>
+        <v>282</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E75" s="2"/>
+      <c r="E75" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F75" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>75</v>
@@ -8676,10 +8837,12 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>248</v>
+        <v>85</v>
       </c>
       <c r="L75" s="2"/>
-      <c r="M75" s="2"/>
+      <c r="M75" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -8705,13 +8868,11 @@
         <v>74</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>74</v>
@@ -8729,26 +8890,1141 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L76" s="2"/>
+      <c r="M76" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L77" s="2"/>
+      <c r="M77" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L78" s="2"/>
+      <c r="M78" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y78" s="2"/>
+      <c r="Z78" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E79" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L79" s="2"/>
+      <c r="M79" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E80" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="F80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L80" s="2"/>
+      <c r="M80" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E81" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="F81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L81" s="2"/>
+      <c r="M81" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E82" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L82" s="2"/>
+      <c r="M82" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L83" s="2"/>
+      <c r="M83" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L84" s="2"/>
+      <c r="M84" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="AG75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK75" t="s" s="2">
+      <c r="S84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L85" s="2"/>
+      <c r="M85" s="2"/>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="L86" s="2"/>
+      <c r="M86" s="2"/>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK86" t="s" s="2">
         <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK75">
+  <autoFilter ref="A1:AK86">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8758,7 +10034,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI74">
+  <conditionalFormatting sqref="A2:AI85">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-traitements.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-traitements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-traitements.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-traitements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
